--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_atacama.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_atacama.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:45</t>
+    <t xml:space="preserve">2026-09-09 20:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_atacama.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_atacama.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:07</t>
+    <t xml:space="preserve">2026-09-18 17:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_atacama.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_atacama.xlsx
@@ -30,33 +30,33 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Caldera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chañaral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huasco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freirina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vallenar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copiapó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diego de Almagro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tierra Amarilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Tierra Amarilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diego de Almagro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copiapó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vallenar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freirina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huasco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chañaral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caldera</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:05</t>
+    <t xml:space="preserve">2026-09-27 21:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -486,13 +486,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5188</v>
+        <v>22273</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5767</v>
+        <v>19746</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>89.96</v>
+        <v>112.8</v>
       </c>
     </row>
     <row r="3">
@@ -500,13 +500,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>13405</v>
+        <v>14699</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>14401</v>
+        <v>13109</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>93.08</v>
+        <v>112.13</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13908</v>
+        <v>12583</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>14137</v>
+        <v>11455</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>98.38</v>
+        <v>109.85</v>
       </c>
     </row>
     <row r="5">
@@ -528,13 +528,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>176599</v>
+        <v>8082</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>174309</v>
+        <v>7779</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>101.31</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>8082</v>
+        <v>176599</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7779</v>
+        <v>174309</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>103.9</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="8">
@@ -570,13 +570,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>12583</v>
+        <v>13908</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>11455</v>
+        <v>14137</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>109.85</v>
+        <v>98.38</v>
       </c>
     </row>
     <row r="9">
@@ -584,13 +584,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>14699</v>
+        <v>13405</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>13109</v>
+        <v>14401</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>112.13</v>
+        <v>93.08</v>
       </c>
     </row>
     <row r="10">
@@ -598,13 +598,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>22273</v>
+        <v>5188</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>19746</v>
+        <v>5767</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>112.8</v>
+        <v>89.96</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_atacama.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_atacama.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:50</t>
+    <t xml:space="preserve">2026-10-05 05:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
